--- a/shared-fixtures/doc-comments/xlsx-note-reference/single-note.xlsx
+++ b/shared-fixtures/doc-comments/xlsx-note-reference/single-note.xlsx
@@ -417,7 +417,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>